--- a/dados/REALIZAR.xlsx
+++ b/dados/REALIZAR.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mv="urn:schemas-microsoft-com:mac:vml">
-  <dimension ref="A1:S122"/>
+  <dimension ref="A1:S95"/>
   <sheetData>
     <row r="1" spans="1:19" customFormat="false">
       <c r="A1" s="1" t="str">
@@ -478,1363 +478,1366 @@
     </row>
     <row r="4" spans="1:15" customFormat="false">
       <c r="A4" s="0" t="str">
-        <v>LIM - UTGC - CONSERVAÇÃO E LIMPEZA - K9</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="B4" s="0" t="str">
-        <v>LIM - UTGC - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C4" s="0" t="str">
-        <v>K9</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="E4" s="0" t="str">
-        <v>normatelprojetoc@gmail.com</v>
+        <v>normatelprojeto740b@gmail.com</v>
       </c>
       <c r="L4" s="0" t="str">
-        <v>11124450</v>
+        <v>11240173</v>
       </c>
       <c r="N4" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O4" s="0" t="str">
-        <v>09/06/2026 11:43:47</v>
+        <v>24/06/2026 10:51:41</v>
       </c>
     </row>
     <row r="5" spans="1:15" customFormat="false">
       <c r="A5" s="0" t="str">
-        <v xml:space="preserve">QLD - UTGSUL - RELATÓRIO FOTOGRÁFICO - K9 UTGC </v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (25/06/2026) (2)</v>
       </c>
       <c r="B5" s="0" t="str">
-        <v>QLD - UTGSUL - RELATÓRIO FOTOGRÁFICO</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C5" s="0" t="str">
-        <v>K9</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E5" s="0" t="str">
-        <v>normatelprojetoc@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
+      </c>
+      <c r="F5" s="0" t="str">
+        <v>25/06/2026 11:00:00</v>
+      </c>
+      <c r="G5" s="0" t="str">
+        <v>25/06/2026 12:00:00</v>
+      </c>
+      <c r="H5" s="0" t="str">
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
+      </c>
+      <c r="J5" s="0" t="str">
+        <v>PROJETO 740 - UTGC</v>
+      </c>
+      <c r="K5" s="0" t="str">
+        <v>3</v>
       </c>
       <c r="L5" s="0" t="str">
-        <v>11124454</v>
+        <v>11243156</v>
       </c>
       <c r="N5" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O5" s="0" t="str">
-        <v>09/06/2026 11:44:12</v>
+        <v>24/06/2026 16:26:29</v>
       </c>
     </row>
     <row r="6" spans="1:15" customFormat="false">
       <c r="A6" s="0" t="str">
-        <v>OPR - TIMS - INSPEÇÃO DO GERADOR NORM - PROJETO TIMS - 745 (22/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (26/06/2026)</v>
       </c>
       <c r="B6" s="0" t="str">
-        <v>OPR - TIMS - INSPEÇÃO DO GERADOR NORM</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C6" s="0" t="str">
-        <v>PROJETO TIMS - 745</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E6" s="0" t="str">
-        <v>equipelimpezatims@gmail.com; gabriel.almeida@normatel.com.br</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F6" s="0" t="str">
-        <v>22/06/2026 01:00:00</v>
+        <v>26/06/2026 11:00:00</v>
       </c>
       <c r="G6" s="0" t="str">
-        <v>27/06/2026 01:00:00</v>
+        <v>26/06/2026 12:00:00</v>
       </c>
       <c r="H6" s="0" t="str">
-        <v>Execução do plano de atividades 'OPR - TIMS - INSPEÇÃO DO GERADOR NORM'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J6" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K6" s="0" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="0" t="str">
-        <v>11217530</v>
+        <v>11243157</v>
       </c>
       <c r="N6" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O6" s="0" t="str">
-        <v>22/06/2026 01:03:09</v>
+        <v>24/06/2026 16:26:29</v>
       </c>
     </row>
     <row r="7" spans="1:15" customFormat="false">
       <c r="A7" s="0" t="str">
-        <v>1 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO MASCULINO - 1 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (29/06/2026)</v>
       </c>
       <c r="B7" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C7" s="0" t="str">
-        <v>K 01 - PORTARIA I - BANHEIRO MASCULINO - 1</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E7" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F7" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>29/06/2026 11:00:00</v>
       </c>
       <c r="G7" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>29/06/2026 12:00:00</v>
       </c>
       <c r="H7" s="0" t="str">
-        <v>Execução do plano de atividades '1 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J7" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K7" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="0" t="str">
-        <v>11227576</v>
+        <v>11243158</v>
       </c>
       <c r="N7" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O7" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:29</v>
       </c>
     </row>
     <row r="8" spans="1:15" customFormat="false">
       <c r="A8" s="0" t="str">
-        <v>2 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO FEMININO - 1 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (30/06/2026)</v>
       </c>
       <c r="B8" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C8" s="0" t="str">
-        <v>K 01 - PORTARIA I - BANHEIRO FEMININO - 1</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E8" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F8" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>30/06/2026 11:00:00</v>
       </c>
       <c r="G8" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>30/06/2026 12:00:00</v>
       </c>
       <c r="H8" s="0" t="str">
-        <v>Execução do plano de atividades '2 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J8" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K8" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="0" t="str">
-        <v>11227577</v>
+        <v>11243159</v>
       </c>
       <c r="N8" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O8" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:29</v>
       </c>
     </row>
     <row r="9" spans="1:15" customFormat="false">
       <c r="A9" s="0" t="str">
-        <v>3 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO MASCULINO - 2 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (02/07/2026)</v>
       </c>
       <c r="B9" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C9" s="0" t="str">
-        <v>K 01 - PORTARIA I - BANHEIRO MASCULINO - 2</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E9" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F9" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>02/07/2026 11:00:00</v>
       </c>
       <c r="G9" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>02/07/2026 12:00:00</v>
       </c>
       <c r="H9" s="0" t="str">
-        <v>Execução do plano de atividades '3 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J9" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K9" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="0" t="str">
-        <v>11227578</v>
+        <v>11243161</v>
       </c>
       <c r="N9" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O9" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:29</v>
       </c>
     </row>
     <row r="10" spans="1:15" customFormat="false">
       <c r="A10" s="0" t="str">
-        <v>4 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO FEMININO - 2 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (03/07/2026)</v>
       </c>
       <c r="B10" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C10" s="0" t="str">
-        <v>K 01 - PORTARIA I - BANHEIRO FEMININO - 2</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E10" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F10" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>03/07/2026 11:00:00</v>
       </c>
       <c r="G10" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>03/07/2026 12:00:00</v>
       </c>
       <c r="H10" s="0" t="str">
-        <v>Execução do plano de atividades '4 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J10" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K10" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="0" t="str">
-        <v>11227579</v>
+        <v>11243162</v>
       </c>
       <c r="N10" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O10" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:29</v>
       </c>
     </row>
     <row r="11" spans="1:15" customFormat="false">
       <c r="A11" s="0" t="str">
-        <v>5 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (06/07/2026)</v>
       </c>
       <c r="B11" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C11" s="0" t="str">
-        <v>K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E11" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F11" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>06/07/2026 11:00:00</v>
       </c>
       <c r="G11" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>06/07/2026 12:00:00</v>
       </c>
       <c r="H11" s="0" t="str">
-        <v>Execução do plano de atividades '5 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J11" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K11" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="0" t="str">
-        <v>11227580</v>
+        <v>11243163</v>
       </c>
       <c r="N11" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O11" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:30</v>
       </c>
     </row>
     <row r="12" spans="1:15" customFormat="false">
       <c r="A12" s="0" t="str">
-        <v>6 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (07/07/2026)</v>
       </c>
       <c r="B12" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C12" s="0" t="str">
-        <v>K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E12" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F12" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>07/07/2026 11:00:00</v>
       </c>
       <c r="G12" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>07/07/2026 12:00:00</v>
       </c>
       <c r="H12" s="0" t="str">
-        <v>Execução do plano de atividades '6 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J12" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K12" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="0" t="str">
-        <v>11227581</v>
+        <v>11243164</v>
       </c>
       <c r="N12" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O12" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:30</v>
       </c>
     </row>
     <row r="13" spans="1:15" customFormat="false">
       <c r="A13" s="0" t="str">
-        <v>7 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (08/07/2026)</v>
       </c>
       <c r="B13" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C13" s="0" t="str">
-        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E13" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F13" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>08/07/2026 11:00:00</v>
       </c>
       <c r="G13" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>08/07/2026 12:00:00</v>
       </c>
       <c r="H13" s="0" t="str">
-        <v>Execução do plano de atividades '7 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J13" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K13" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="0" t="str">
-        <v>11227582</v>
+        <v>11243165</v>
       </c>
       <c r="N13" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O13" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:30</v>
       </c>
     </row>
     <row r="14" spans="1:15" customFormat="false">
       <c r="A14" s="0" t="str">
-        <v>8 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (09/07/2026)</v>
       </c>
       <c r="B14" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C14" s="0" t="str">
-        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E14" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F14" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>09/07/2026 11:00:00</v>
       </c>
       <c r="G14" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>09/07/2026 12:00:00</v>
       </c>
       <c r="H14" s="0" t="str">
-        <v>Execução do plano de atividades '8 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J14" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K14" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="0" t="str">
-        <v>11227583</v>
+        <v>11243166</v>
       </c>
       <c r="N14" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O14" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:30</v>
       </c>
     </row>
     <row r="15" spans="1:15" customFormat="false">
       <c r="A15" s="0" t="str">
-        <v>9 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 04 - VIVÊNCIA - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (10/07/2026)</v>
       </c>
       <c r="B15" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C15" s="0" t="str">
-        <v>K 04 - VIVÊNCIA - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E15" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F15" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>10/07/2026 11:00:00</v>
       </c>
       <c r="G15" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>10/07/2026 12:00:00</v>
       </c>
       <c r="H15" s="0" t="str">
-        <v>Execução do plano de atividades '9 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J15" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K15" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="0" t="str">
-        <v>11227584</v>
+        <v>11243167</v>
       </c>
       <c r="N15" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O15" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:30</v>
       </c>
     </row>
     <row r="16" spans="1:15" customFormat="false">
       <c r="A16" s="0" t="str">
-        <v>10 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 04 - VIVÊNCIA - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (13/07/2026)</v>
       </c>
       <c r="B16" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C16" s="0" t="str">
-        <v>K 04 - VIVÊNCIA - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E16" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F16" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>13/07/2026 11:00:00</v>
       </c>
       <c r="G16" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>13/07/2026 12:00:00</v>
       </c>
       <c r="H16" s="0" t="str">
-        <v>Execução do plano de atividades '10 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J16" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K16" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="0" t="str">
-        <v>11227585</v>
+        <v>11243168</v>
       </c>
       <c r="N16" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O16" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:30</v>
       </c>
     </row>
     <row r="17" spans="1:15" customFormat="false">
       <c r="A17" s="0" t="str">
-        <v>11 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (14/07/2026)</v>
       </c>
       <c r="B17" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C17" s="0" t="str">
-        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E17" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F17" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 11:00:00</v>
       </c>
       <c r="G17" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 12:00:00</v>
       </c>
       <c r="H17" s="0" t="str">
-        <v>Execução do plano de atividades '11 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J17" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K17" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="0" t="str">
-        <v>11227586</v>
+        <v>11243169</v>
       </c>
       <c r="N17" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O17" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:31</v>
       </c>
     </row>
     <row r="18" spans="1:15" customFormat="false">
       <c r="A18" s="0" t="str">
-        <v>12 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (15/07/2026)</v>
       </c>
       <c r="B18" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C18" s="0" t="str">
-        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E18" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F18" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>15/07/2026 11:00:00</v>
       </c>
       <c r="G18" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>15/07/2026 12:00:00</v>
       </c>
       <c r="H18" s="0" t="str">
-        <v>Execução do plano de atividades '12 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J18" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K18" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" s="0" t="str">
-        <v>11227587</v>
+        <v>11243170</v>
       </c>
       <c r="N18" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O18" s="0" t="str">
-        <v>23/06/2026 01:02:23</v>
+        <v>24/06/2026 16:26:31</v>
       </c>
     </row>
     <row r="19" spans="1:15" customFormat="false">
       <c r="A19" s="0" t="str">
-        <v>13 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (16/07/2026)</v>
       </c>
       <c r="B19" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C19" s="0" t="str">
-        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E19" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F19" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>16/07/2026 11:00:00</v>
       </c>
       <c r="G19" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>16/07/2026 12:00:00</v>
       </c>
       <c r="H19" s="0" t="str">
-        <v>Execução do plano de atividades '13 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J19" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K19" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" s="0" t="str">
-        <v>11227588</v>
+        <v>11243171</v>
       </c>
       <c r="N19" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O19" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>24/06/2026 16:26:31</v>
       </c>
     </row>
     <row r="20" spans="1:15" customFormat="false">
       <c r="A20" s="0" t="str">
-        <v>14 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (17/07/2026)</v>
       </c>
       <c r="B20" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C20" s="0" t="str">
-        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E20" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F20" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>17/07/2026 11:00:00</v>
       </c>
       <c r="G20" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>17/07/2026 12:00:00</v>
       </c>
       <c r="H20" s="0" t="str">
-        <v>Execução do plano de atividades '14 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J20" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K20" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20" s="0" t="str">
-        <v>11227589</v>
+        <v>11243172</v>
       </c>
       <c r="N20" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O20" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>24/06/2026 16:26:31</v>
       </c>
     </row>
     <row r="21" spans="1:15" customFormat="false">
       <c r="A21" s="0" t="str">
-        <v>15 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 08 - ALMOXARIFADO - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (20/07/2026)</v>
       </c>
       <c r="B21" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C21" s="0" t="str">
-        <v>K 08 - ALMOXARIFADO - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E21" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F21" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>20/07/2026 11:00:00</v>
       </c>
       <c r="G21" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>20/07/2026 12:00:00</v>
       </c>
       <c r="H21" s="0" t="str">
-        <v>Execução do plano de atividades '15 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J21" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K21" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" s="0" t="str">
-        <v>11227590</v>
+        <v>11243173</v>
       </c>
       <c r="N21" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O21" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>24/06/2026 16:26:31</v>
       </c>
     </row>
     <row r="22" spans="1:15" customFormat="false">
       <c r="A22" s="0" t="str">
-        <v>16 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 08 - ALMOXARIFADO - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (21/07/2026)</v>
       </c>
       <c r="B22" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C22" s="0" t="str">
-        <v>K 08 - ALMOXARIFADO - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E22" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F22" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>21/07/2026 11:00:00</v>
       </c>
       <c r="G22" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>21/07/2026 12:00:00</v>
       </c>
       <c r="H22" s="0" t="str">
-        <v>Execução do plano de atividades '16 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J22" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K22" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" s="0" t="str">
-        <v>11227591</v>
+        <v>11243174</v>
       </c>
       <c r="N22" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O22" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>24/06/2026 16:26:32</v>
       </c>
     </row>
     <row r="23" spans="1:15" customFormat="false">
       <c r="A23" s="0" t="str">
-        <v>17 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 09 - ALMOXARIFADO - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (22/07/2026)</v>
       </c>
       <c r="B23" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C23" s="0" t="str">
-        <v>K 09 - ALMOXARIFADO - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E23" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F23" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>22/07/2026 11:00:00</v>
       </c>
       <c r="G23" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
       <c r="H23" s="0" t="str">
-        <v>Execução do plano de atividades '17 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J23" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K23" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="0" t="str">
-        <v>11227592</v>
+        <v>11243175</v>
       </c>
       <c r="N23" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O23" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>24/06/2026 16:26:32</v>
       </c>
     </row>
     <row r="24" spans="1:15" customFormat="false">
       <c r="A24" s="0" t="str">
-        <v>18 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 09 - ALMOXARIFADO - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (23/07/2026)</v>
       </c>
       <c r="B24" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C24" s="0" t="str">
-        <v>K 09 - ALMOXARIFADO - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E24" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F24" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>23/07/2026 11:00:00</v>
       </c>
       <c r="G24" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>23/07/2026 12:00:00</v>
       </c>
       <c r="H24" s="0" t="str">
-        <v>Execução do plano de atividades '18 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J24" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K24" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L24" s="0" t="str">
-        <v>11227593</v>
+        <v>11243176</v>
       </c>
       <c r="N24" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O24" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>24/06/2026 16:26:32</v>
       </c>
     </row>
     <row r="25" spans="1:15" customFormat="false">
       <c r="A25" s="0" t="str">
-        <v>19 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 10 - MANUTENÇÃO - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (24/07/2026)</v>
       </c>
       <c r="B25" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C25" s="0" t="str">
-        <v>K 10 - MANUTENÇÃO - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E25" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F25" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>24/07/2026 11:00:00</v>
       </c>
       <c r="G25" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>24/07/2026 12:00:00</v>
       </c>
       <c r="H25" s="0" t="str">
-        <v>Execução do plano de atividades '19 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J25" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K25" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L25" s="0" t="str">
-        <v>11227594</v>
+        <v>11243177</v>
       </c>
       <c r="N25" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O25" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>24/06/2026 16:26:32</v>
       </c>
     </row>
     <row r="26" spans="1:15" customFormat="false">
       <c r="A26" s="0" t="str">
-        <v>20 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 10 - MANUTENÇÃO - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (27/07/2026)</v>
       </c>
       <c r="B26" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C26" s="0" t="str">
-        <v>K 10 - MANUTENÇÃO - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E26" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F26" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>27/07/2026 11:00:00</v>
       </c>
       <c r="G26" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>27/07/2026 12:00:00</v>
       </c>
       <c r="H26" s="0" t="str">
-        <v>Execução do plano de atividades '20 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J26" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K26" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="0" t="str">
-        <v>11227595</v>
+        <v>11265233</v>
       </c>
       <c r="N26" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O26" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>27/06/2026 01:02:07</v>
       </c>
     </row>
     <row r="27" spans="1:15" customFormat="false">
       <c r="A27" s="0" t="str">
-        <v>21 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 11 - LABORATÓRIO - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (28/07/2026)</v>
       </c>
       <c r="B27" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C27" s="0" t="str">
-        <v>K 11 - LABORATÓRIO - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E27" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F27" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>28/07/2026 11:00:00</v>
       </c>
       <c r="G27" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>28/07/2026 12:00:00</v>
       </c>
       <c r="H27" s="0" t="str">
-        <v>Execução do plano de atividades '21 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J27" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K27" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" s="0" t="str">
-        <v>11227596</v>
+        <v>11267844</v>
       </c>
       <c r="N27" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O27" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>28/06/2026 01:01:42</v>
       </c>
     </row>
     <row r="28" spans="1:15" customFormat="false">
       <c r="A28" s="0" t="str">
-        <v>22 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 11 - LABORATÓRIO - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (29/07/2026)</v>
       </c>
       <c r="B28" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C28" s="0" t="str">
-        <v>K 11 - LABORATÓRIO - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E28" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F28" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>29/07/2026 11:00:00</v>
       </c>
       <c r="G28" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>29/07/2026 12:00:00</v>
       </c>
       <c r="H28" s="0" t="str">
-        <v>Execução do plano de atividades '22 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J28" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K28" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="0" t="str">
-        <v>11227597</v>
+        <v>11270177</v>
       </c>
       <c r="N28" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O28" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>29/06/2026 01:02:31</v>
       </c>
     </row>
     <row r="29" spans="1:15" customFormat="false">
       <c r="A29" s="0" t="str">
-        <v>23 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 1 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (30/07/2026)</v>
       </c>
       <c r="B29" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C29" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 1</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E29" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F29" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>30/07/2026 11:00:00</v>
       </c>
       <c r="G29" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>30/07/2026 12:00:00</v>
       </c>
       <c r="H29" s="0" t="str">
-        <v>Execução do plano de atividades '23 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J29" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K29" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="0" t="str">
-        <v>11227598</v>
+        <v>11278137</v>
       </c>
       <c r="N29" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O29" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>30/06/2026 01:02:42</v>
       </c>
     </row>
     <row r="30" spans="1:15" customFormat="false">
       <c r="A30" s="0" t="str">
-        <v>24 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 2 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (31/07/2026)</v>
       </c>
       <c r="B30" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C30" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 2</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E30" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F30" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>31/07/2026 11:00:00</v>
       </c>
       <c r="G30" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>31/07/2026 12:00:00</v>
       </c>
       <c r="H30" s="0" t="str">
-        <v>Execução do plano de atividades '24 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J30" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K30" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="0" t="str">
-        <v>11227599</v>
+        <v>11288819</v>
       </c>
       <c r="N30" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O30" s="0" t="str">
-        <v>23/06/2026 01:02:24</v>
+        <v>01/07/2026 01:02:41</v>
       </c>
     </row>
     <row r="31" spans="1:15" customFormat="false">
       <c r="A31" s="0" t="str">
-        <v>25 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 3 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (03/08/2026)</v>
       </c>
       <c r="B31" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C31" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 3</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E31" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F31" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>03/08/2026 11:00:00</v>
       </c>
       <c r="G31" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>03/08/2026 12:00:00</v>
       </c>
       <c r="H31" s="0" t="str">
-        <v>Execução do plano de atividades '25 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J31" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K31" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="0" t="str">
-        <v>11227600</v>
+        <v>11321423</v>
       </c>
       <c r="N31" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O31" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>04/07/2026 01:02:12</v>
       </c>
     </row>
     <row r="32" spans="1:15" customFormat="false">
       <c r="A32" s="0" t="str">
-        <v>26 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 1 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (04/08/2026)</v>
       </c>
       <c r="B32" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C32" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 1</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E32" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F32" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>04/08/2026 11:00:00</v>
       </c>
       <c r="G32" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>04/08/2026 12:00:00</v>
       </c>
       <c r="H32" s="0" t="str">
-        <v>Execução do plano de atividades '26 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J32" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K32" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L32" s="0" t="str">
-        <v>11227601</v>
+        <v>11323997</v>
       </c>
       <c r="N32" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O32" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>05/07/2026 01:01:45</v>
       </c>
     </row>
     <row r="33" spans="1:15" customFormat="false">
       <c r="A33" s="0" t="str">
-        <v>27 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 2 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (05/08/2026)</v>
       </c>
       <c r="B33" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C33" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 2</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E33" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F33" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>05/08/2026 11:00:00</v>
       </c>
       <c r="G33" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>05/08/2026 12:00:00</v>
       </c>
       <c r="H33" s="0" t="str">
-        <v>Execução do plano de atividades '27 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J33" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K33" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="0" t="str">
-        <v>11227602</v>
+        <v>11326208</v>
       </c>
       <c r="N33" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O33" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>06/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="34" spans="1:15" customFormat="false">
       <c r="A34" s="0" t="str">
-        <v>28 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 3 (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (06/08/2026)</v>
       </c>
       <c r="B34" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C34" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 3</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E34" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F34" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>06/08/2026 11:00:00</v>
       </c>
       <c r="G34" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>06/08/2026 12:00:00</v>
       </c>
       <c r="H34" s="0" t="str">
-        <v>Execução do plano de atividades '28 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J34" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K34" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="0" t="str">
-        <v>11227603</v>
+        <v>11338599</v>
       </c>
       <c r="N34" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O34" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>07/07/2026 01:02:49</v>
       </c>
     </row>
     <row r="35" spans="1:15" customFormat="false">
       <c r="A35" s="0" t="str">
-        <v>29 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 19 - TI / TCOM - BANHEIRO UNISSEX (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (07/08/2026)</v>
       </c>
       <c r="B35" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C35" s="0" t="str">
-        <v>K 19 - TI / TCOM - BANHEIRO UNISSEX</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E35" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F35" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>07/08/2026 11:00:00</v>
       </c>
       <c r="G35" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>07/08/2026 12:00:00</v>
       </c>
       <c r="H35" s="0" t="str">
-        <v>Execução do plano de atividades '29 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J35" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K35" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="0" t="str">
-        <v>11227604</v>
+        <v>11348599</v>
       </c>
       <c r="N35" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O35" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>08/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="36" spans="1:15" customFormat="false">
       <c r="A36" s="0" t="str">
-        <v>30 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 31 - PORTARIA II - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (10/08/2026)</v>
       </c>
       <c r="B36" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C36" s="0" t="str">
-        <v>K 31 - PORTARIA II - BANHEIRO MASCULINO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E36" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F36" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>10/08/2026 11:00:00</v>
       </c>
       <c r="G36" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>10/08/2026 12:00:00</v>
       </c>
       <c r="H36" s="0" t="str">
-        <v>Execução do plano de atividades '30 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J36" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K36" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="0" t="str">
-        <v>11227605</v>
+        <v>11376914</v>
       </c>
       <c r="N36" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O36" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>11/07/2026 01:02:09</v>
       </c>
     </row>
     <row r="37" spans="1:15" customFormat="false">
       <c r="A37" s="0" t="str">
-        <v>31 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 31 - PORTARIA II - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (11/08/2026)</v>
       </c>
       <c r="B37" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C37" s="0" t="str">
-        <v>K 31 - PORTARIA II - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E37" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F37" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>11/08/2026 11:00:00</v>
       </c>
       <c r="G37" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>11/08/2026 12:00:00</v>
       </c>
       <c r="H37" s="0" t="str">
-        <v>Execução do plano de atividades '31 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J37" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K37" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L37" s="0" t="str">
-        <v>11227606</v>
+        <v>11379702</v>
       </c>
       <c r="N37" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O37" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>12/07/2026 01:01:46</v>
       </c>
     </row>
     <row r="38" spans="1:15" customFormat="false">
       <c r="A38" s="0" t="str">
-        <v>1 - LIM - UTGSUL - COPA - K 01 - PORTARIA I - COPA (23/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (12/08/2026)</v>
       </c>
       <c r="B38" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C38" s="0" t="str">
-        <v>K 01 - PORTARIA I - COPA</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E38" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
       </c>
       <c r="F38" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>12/08/2026 11:00:00</v>
       </c>
       <c r="G38" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>12/08/2026 12:00:00</v>
       </c>
       <c r="H38" s="0" t="str">
-        <v>Execução do plano de atividades '1 - LIM - UTGSUL - COPA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J38" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K38" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" s="0" t="str">
-        <v>11227607</v>
+        <v>11381885</v>
       </c>
       <c r="N38" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O38" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>13/07/2026 01:02:53</v>
       </c>
     </row>
     <row r="39" spans="1:15" customFormat="false">
       <c r="A39" s="0" t="str">
-        <v>2 - LIM - UTGSUL - COPA - K 02 - ABRIGO PARA MOTORISTAS - COPA (23/06/2026)</v>
+        <v>Verificar um SN</v>
       </c>
       <c r="B39" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>QLD - UTGC - RELATÓRIO DE SERVICE NOW - Ueslei</v>
       </c>
       <c r="C39" s="0" t="str">
-        <v>K 02 - ABRIGO PARA MOTORISTAS - COPA</v>
+        <v>K-32</v>
       </c>
       <c r="E39" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>utgsulnormatel@gmail.com</v>
       </c>
       <c r="F39" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>13/07/2026 10:56:09</v>
       </c>
       <c r="G39" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
-      </c>
-      <c r="H39" s="0" t="str">
-        <v>Execução do plano de atividades '2 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J39" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K39" s="0" t="str">
-        <v>2</v>
+        <v>13/07/2026 14:56:09</v>
       </c>
       <c r="L39" s="0" t="str">
-        <v>11227608</v>
+        <v>11386059</v>
       </c>
       <c r="N39" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O39" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>13/07/2026 10:33:36</v>
       </c>
     </row>
     <row r="40" spans="1:15" customFormat="false">
       <c r="A40" s="0" t="str">
-        <v>3 - LIM - UTGSUL - COPA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - COPA (23/06/2026)</v>
+        <v>1 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO MASCULINO - 1 (14/07/2026)</v>
       </c>
       <c r="B40" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C40" s="0" t="str">
-        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - COPA</v>
+        <v>K 01 - PORTARIA I - BANHEIRO MASCULINO - 1</v>
       </c>
       <c r="E40" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F40" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G40" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H40" s="0" t="str">
-        <v>Execução do plano de atividades '3 - LIM - UTGSUL - COPA'.</v>
+        <v>Execução do plano de atividades '1 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J40" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -1843,36 +1846,36 @@
         <v>2</v>
       </c>
       <c r="L40" s="0" t="str">
-        <v>11227609</v>
+        <v>11392289</v>
       </c>
       <c r="N40" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O40" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="41" spans="1:15" customFormat="false">
       <c r="A41" s="0" t="str">
-        <v>4 - LIM - UTGSUL - COPA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - COPA (23/06/2026)</v>
+        <v>2 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO FEMININO - 1 (14/07/2026)</v>
       </c>
       <c r="B41" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C41" s="0" t="str">
-        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - COPA</v>
+        <v>K 01 - PORTARIA I - BANHEIRO FEMININO - 1</v>
       </c>
       <c r="E41" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F41" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G41" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H41" s="0" t="str">
-        <v>Execução do plano de atividades '4 - LIM - UTGSUL - COPA'.</v>
+        <v>Execução do plano de atividades '2 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J41" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -1881,36 +1884,36 @@
         <v>2</v>
       </c>
       <c r="L41" s="0" t="str">
-        <v>11227610</v>
+        <v>11392290</v>
       </c>
       <c r="N41" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O41" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="42" spans="1:15" customFormat="false">
       <c r="A42" s="0" t="str">
-        <v>5 - LIM - UTGSUL - COPA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - COPA (23/06/2026)</v>
+        <v>3 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO MASCULINO - 2 (14/07/2026)</v>
       </c>
       <c r="B42" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C42" s="0" t="str">
-        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - COPA</v>
+        <v>K 01 - PORTARIA I - BANHEIRO MASCULINO - 2</v>
       </c>
       <c r="E42" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F42" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G42" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H42" s="0" t="str">
-        <v>Execução do plano de atividades '5 - LIM - UTGSUL - COPA'.</v>
+        <v>Execução do plano de atividades '3 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J42" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -1919,36 +1922,36 @@
         <v>2</v>
       </c>
       <c r="L42" s="0" t="str">
-        <v>11227611</v>
+        <v>11392291</v>
       </c>
       <c r="N42" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O42" s="0" t="str">
-        <v>23/06/2026 01:02:25</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="43" spans="1:15" customFormat="false">
       <c r="A43" s="0" t="str">
-        <v>6 - LIM - UTGSUL - COPA - K 08 - ALMOXARIFADO - COPA (23/06/2026)</v>
+        <v>4 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO FEMININO - 2 (14/07/2026)</v>
       </c>
       <c r="B43" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C43" s="0" t="str">
-        <v>K 08 - ALMOXARIFADO - COPA</v>
+        <v>K 01 - PORTARIA I - BANHEIRO FEMININO - 2</v>
       </c>
       <c r="E43" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F43" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G43" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H43" s="0" t="str">
-        <v>Execução do plano de atividades '6 - LIM - UTGSUL - COPA'.</v>
+        <v>Execução do plano de atividades '4 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J43" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -1957,36 +1960,36 @@
         <v>2</v>
       </c>
       <c r="L43" s="0" t="str">
-        <v>11227612</v>
+        <v>11392292</v>
       </c>
       <c r="N43" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O43" s="0" t="str">
-        <v>23/06/2026 01:02:26</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="44" spans="1:15" customFormat="false">
       <c r="A44" s="0" t="str">
-        <v>7 - LIM - UTGSUL - COPA - K 09 - ALMOXARIFADO - COPA (23/06/2026)</v>
+        <v>5 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B44" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C44" s="0" t="str">
-        <v>K 09 - ALMOXARIFADO - COPA</v>
+        <v>K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO MASCULINO</v>
       </c>
       <c r="E44" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F44" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G44" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H44" s="0" t="str">
-        <v>Execução do plano de atividades '7 - LIM - UTGSUL - COPA'.</v>
+        <v>Execução do plano de atividades '5 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J44" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -1995,36 +1998,36 @@
         <v>2</v>
       </c>
       <c r="L44" s="0" t="str">
-        <v>11227613</v>
+        <v>11392293</v>
       </c>
       <c r="N44" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O44" s="0" t="str">
-        <v>23/06/2026 01:02:26</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="45" spans="1:15" customFormat="false">
       <c r="A45" s="0" t="str">
-        <v>8 - LIM - UTGSUL - COPA - K 10 - MANUTENÇÃO - COPA (23/06/2026)</v>
+        <v>6 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B45" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C45" s="0" t="str">
-        <v>K 10 - MANUTENÇÃO - COPA</v>
+        <v>K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO FEMININO</v>
       </c>
       <c r="E45" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F45" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G45" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H45" s="0" t="str">
-        <v>Execução do plano de atividades '8 - LIM - UTGSUL - COPA'.</v>
+        <v>Execução do plano de atividades '6 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J45" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2033,36 +2036,36 @@
         <v>2</v>
       </c>
       <c r="L45" s="0" t="str">
-        <v>11227614</v>
+        <v>11392294</v>
       </c>
       <c r="N45" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O45" s="0" t="str">
-        <v>23/06/2026 01:02:26</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="46" spans="1:15" customFormat="false">
       <c r="A46" s="0" t="str">
-        <v>9 - LIM - UTGSUL - COPA - K 11 - LABORATÓRIO - COPA (23/06/2026)</v>
+        <v>7 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B46" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C46" s="0" t="str">
-        <v>K 11 - LABORATÓRIO - COPA</v>
+        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO MASCULINO</v>
       </c>
       <c r="E46" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F46" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G46" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H46" s="0" t="str">
-        <v>Execução do plano de atividades '9 - LIM - UTGSUL - COPA'.</v>
+        <v>Execução do plano de atividades '7 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J46" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2071,693 +2074,720 @@
         <v>2</v>
       </c>
       <c r="L46" s="0" t="str">
-        <v>11227615</v>
+        <v>11392295</v>
       </c>
       <c r="N46" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O46" s="0" t="str">
-        <v>23/06/2026 01:02:26</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="47" spans="1:15" customFormat="false">
       <c r="A47" s="0" t="str">
-        <v>19 - LIM - TIMS - LIMPEZA DAS SALAS - IMÓVEL AL 08 - SALA ADMINISTRATIVA (23/06/2026)</v>
+        <v>8 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B47" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C47" s="0" t="str">
-        <v>IMÓVEL AL 08 - SALA ADMINISTRATIVA</v>
+        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO FEMININO</v>
+      </c>
+      <c r="E47" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F47" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G47" s="0" t="str">
-        <v>24/06/2026 00:20:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H47" s="0" t="str">
-        <v>Execução do plano de atividades '19 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
+        <v>Execução do plano de atividades '8 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J47" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K47" s="0" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="0" t="str">
-        <v>11227640</v>
+        <v>11392296</v>
       </c>
       <c r="N47" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O47" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="48" spans="1:15" customFormat="false">
       <c r="A48" s="0" t="str">
-        <v>1 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>9 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 04 - VIVÊNCIA - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B48" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C48" s="0" t="str">
-        <v>GALPÃO BASERV - BANHEIRO MASCULINO</v>
+        <v>K 04 - VIVÊNCIA - BANHEIRO MASCULINO</v>
       </c>
       <c r="E48" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F48" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G48" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H48" s="0" t="str">
-        <v>Execução do plano de atividades '1 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '9 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J48" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K48" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L48" s="0" t="str">
-        <v>11227641</v>
+        <v>11392297</v>
       </c>
       <c r="N48" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O48" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="49" spans="1:15" customFormat="false">
       <c r="A49" s="0" t="str">
-        <v>2 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>10 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 04 - VIVÊNCIA - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B49" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C49" s="0" t="str">
-        <v>GALPÃO BASERV - BANHEIRO FEMININO</v>
+        <v>K 04 - VIVÊNCIA - BANHEIRO FEMININO</v>
       </c>
       <c r="E49" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F49" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G49" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H49" s="0" t="str">
-        <v>Execução do plano de atividades '2 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '10 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J49" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K49" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L49" s="0" t="str">
-        <v>11227642</v>
+        <v>11392298</v>
       </c>
       <c r="N49" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O49" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="50" spans="1:15" customFormat="false">
       <c r="A50" s="0" t="str">
-        <v>3 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO UNISSEX (23/06/2026)</v>
+        <v>11 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B50" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C50" s="0" t="str">
-        <v>GALPÃO BASERV - BANHEIRO UNISSEX</v>
+        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO MASCULINO</v>
       </c>
       <c r="E50" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F50" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G50" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H50" s="0" t="str">
-        <v>Execução do plano de atividades '3 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '11 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J50" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K50" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L50" s="0" t="str">
-        <v>11227643</v>
+        <v>11392299</v>
       </c>
       <c r="N50" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O50" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="51" spans="1:15" customFormat="false">
       <c r="A51" s="0" t="str">
-        <v>4 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - BRIGADA - CONTÊINER - BANHEIRO UNISSEX (23/06/2026)</v>
+        <v>12 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B51" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C51" s="0" t="str">
-        <v>BRIGADA - CONTÊINER - BANHEIRO UNISSEX</v>
+        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO FEMININO</v>
       </c>
       <c r="E51" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F51" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G51" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H51" s="0" t="str">
-        <v>Execução do plano de atividades '4 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '12 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J51" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K51" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L51" s="0" t="str">
-        <v>11227644</v>
+        <v>11392300</v>
       </c>
       <c r="N51" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O51" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:30</v>
       </c>
     </row>
     <row r="52" spans="1:15" customFormat="false">
       <c r="A52" s="0" t="str">
-        <v>5 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>13 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B52" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C52" s="0" t="str">
-        <v>IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO MASCULINO</v>
+        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO MASCULINO</v>
       </c>
       <c r="E52" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F52" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G52" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H52" s="0" t="str">
-        <v>Execução do plano de atividades '5 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '13 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J52" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K52" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L52" s="0" t="str">
-        <v>11227645</v>
+        <v>11392301</v>
       </c>
       <c r="N52" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O52" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="53" spans="1:15" customFormat="false">
       <c r="A53" s="0" t="str">
-        <v>6 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO FEMININO (23/06/2026)</v>
+        <v>14 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B53" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C53" s="0" t="str">
-        <v>IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO FEMININO</v>
+        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO FEMININO</v>
       </c>
       <c r="E53" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F53" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G53" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H53" s="0" t="str">
-        <v>Execução do plano de atividades '6 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '14 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J53" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K53" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L53" s="0" t="str">
-        <v>11227646</v>
+        <v>11392302</v>
       </c>
       <c r="N53" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O53" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="54" spans="1:15" customFormat="false">
       <c r="A54" s="0" t="str">
-        <v>7 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - GUARITA - BANHEIRO UNISSEX (23/06/2026)</v>
+        <v>15 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 08 - ALMOXARIFADO - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B54" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C54" s="0" t="str">
-        <v>IMÓVEL AL 08 - GUARITA - BANHEIRO UNISSEX</v>
+        <v>K 08 - ALMOXARIFADO - BANHEIRO MASCULINO</v>
       </c>
       <c r="E54" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F54" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G54" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H54" s="0" t="str">
-        <v>Execução do plano de atividades '7 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '15 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J54" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K54" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L54" s="0" t="str">
-        <v>11227647</v>
+        <v>11392303</v>
       </c>
       <c r="N54" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O54" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="55" spans="1:15" customFormat="false">
       <c r="A55" s="0" t="str">
-        <v>8 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - VESTIÁRIO - BANHEIRO MASCULINO (23/06/2026)</v>
+        <v>16 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 08 - ALMOXARIFADO - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B55" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C55" s="0" t="str">
-        <v>VESTIÁRIO - BANHEIRO MASCULINO</v>
+        <v>K 08 - ALMOXARIFADO - BANHEIRO FEMININO</v>
       </c>
       <c r="E55" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F55" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G55" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H55" s="0" t="str">
-        <v>Execução do plano de atividades '8 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '16 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J55" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K55" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L55" s="0" t="str">
-        <v>11227648</v>
+        <v>11392304</v>
       </c>
       <c r="N55" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O55" s="0" t="str">
-        <v>23/06/2026 01:02:29</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="56" spans="1:15" customFormat="false">
       <c r="A56" s="0" t="str">
-        <v>9 - LIM - TIMS - LIMPEZA DO REFEITÓRIO - GALPÃO BASERV - REFEITÓRIO (23/06/2026)</v>
+        <v>17 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 09 - ALMOXARIFADO - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B56" s="0" t="str">
-        <v>LIM - TIMS - REFEITÓRIO</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C56" s="0" t="str">
-        <v>GALPÃO BASERV - REFEITÓRIO</v>
+        <v>K 09 - ALMOXARIFADO - BANHEIRO MASCULINO</v>
+      </c>
+      <c r="E56" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F56" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G56" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H56" s="0" t="str">
-        <v>Execução do plano de atividades '9 - LIM - TIMS - LIMPEZA DO REFEITÓRIO'.</v>
+        <v>Execução do plano de atividades '17 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J56" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K56" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L56" s="0" t="str">
-        <v>11227649</v>
+        <v>11392305</v>
       </c>
       <c r="N56" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O56" s="0" t="str">
-        <v>23/06/2026 01:02:30</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="57" spans="1:15" customFormat="false">
       <c r="A57" s="0" t="str">
-        <v>10 - LIM - TIMS - LIMPEZA DO REFEITÓRIO - IMÓVEL AL 08 - REFEITÓRIO (23/06/2026)</v>
+        <v>18 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 09 - ALMOXARIFADO - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B57" s="0" t="str">
-        <v>LIM - TIMS - REFEITÓRIO</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C57" s="0" t="str">
-        <v>IMÓVEL AL 08 - REFEITÓRIO</v>
+        <v>K 09 - ALMOXARIFADO - BANHEIRO FEMININO</v>
+      </c>
+      <c r="E57" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F57" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G57" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H57" s="0" t="str">
-        <v>Execução do plano de atividades '10 - LIM - TIMS - LIMPEZA DO REFEITÓRIO'.</v>
+        <v>Execução do plano de atividades '18 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J57" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K57" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L57" s="0" t="str">
-        <v>11227650</v>
+        <v>11392306</v>
       </c>
       <c r="N57" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O57" s="0" t="str">
-        <v>23/06/2026 01:02:30</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="58" spans="1:15" customFormat="false">
       <c r="A58" s="0" t="str">
-        <v>11 - LIM - TIMS - LIMPEZA DA COPA - GALPÃO BASERV - COPA (23/06/2026)</v>
+        <v>19 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 10 - MANUTENÇÃO - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B58" s="0" t="str">
-        <v>LIM - TIMS - COPA</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C58" s="0" t="str">
-        <v>GALPÃO BASERV - COPA</v>
+        <v>K 10 - MANUTENÇÃO - BANHEIRO MASCULINO</v>
+      </c>
+      <c r="E58" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F58" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G58" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H58" s="0" t="str">
-        <v>Execução do plano de atividades '11 - LIM - TIMS - LIMPEZA DA COPA'.</v>
+        <v>Execução do plano de atividades '19 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J58" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K58" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L58" s="0" t="str">
-        <v>11227651</v>
+        <v>11392307</v>
       </c>
       <c r="N58" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O58" s="0" t="str">
-        <v>23/06/2026 01:02:30</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="59" spans="1:15" customFormat="false">
       <c r="A59" s="0" t="str">
-        <v>12 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - GUARITA (23/06/2026)</v>
+        <v>20 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 10 - MANUTENÇÃO - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B59" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C59" s="0" t="str">
-        <v>GALPÃO BASERV - GUARITA</v>
+        <v>K 10 - MANUTENÇÃO - BANHEIRO FEMININO</v>
+      </c>
+      <c r="E59" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F59" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G59" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H59" s="0" t="str">
-        <v>Execução do plano de atividades '12 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
+        <v>Execução do plano de atividades '20 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J59" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K59" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L59" s="0" t="str">
-        <v>11227652</v>
+        <v>11392308</v>
       </c>
       <c r="N59" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O59" s="0" t="str">
-        <v>23/06/2026 01:02:30</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="60" spans="1:15" customFormat="false">
       <c r="A60" s="0" t="str">
-        <v>13 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - SALA DE ADMINISTRAÇÃO (23/06/2026)</v>
+        <v>21 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 11 - LABORATÓRIO - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B60" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C60" s="0" t="str">
-        <v>GALPÃO BASERV - SALA DE ADMINISTRAÇÃO</v>
+        <v>K 11 - LABORATÓRIO - BANHEIRO MASCULINO</v>
+      </c>
+      <c r="E60" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F60" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G60" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H60" s="0" t="str">
-        <v>Execução do plano de atividades '13 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
+        <v>Execução do plano de atividades '21 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J60" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K60" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L60" s="0" t="str">
-        <v>11227653</v>
+        <v>11392309</v>
       </c>
       <c r="N60" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O60" s="0" t="str">
-        <v>23/06/2026 01:02:30</v>
+        <v>14/07/2026 01:02:31</v>
       </c>
     </row>
     <row r="61" spans="1:15" customFormat="false">
       <c r="A61" s="0" t="str">
-        <v>14 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - SALA DA BRIGADA (23/06/2026)</v>
+        <v>22 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 11 - LABORATÓRIO - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B61" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C61" s="0" t="str">
-        <v>GALPÃO BASERV - SALA DA BRIGADA</v>
+        <v>K 11 - LABORATÓRIO - BANHEIRO FEMININO</v>
+      </c>
+      <c r="E61" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F61" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G61" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H61" s="0" t="str">
-        <v>Execução do plano de atividades '14 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
+        <v>Execução do plano de atividades '22 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J61" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K61" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L61" s="0" t="str">
-        <v>11227654</v>
+        <v>11392310</v>
       </c>
       <c r="N61" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O61" s="0" t="str">
-        <v>23/06/2026 01:02:30</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="62" spans="1:15" customFormat="false">
       <c r="A62" s="0" t="str">
-        <v>17 - LIM - TIMS - LIMPEZA DAS SALAS - NORMATEL - SALA DE ADMINISTRAÇÃO (23/06/2026)</v>
+        <v>23 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 1 (14/07/2026)</v>
       </c>
       <c r="B62" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C62" s="0" t="str">
-        <v>NORMATEL - SALA DE ADMINISTRAÇÃO</v>
+        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 1</v>
+      </c>
+      <c r="E62" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F62" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G62" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H62" s="0" t="str">
-        <v>Execução do plano de atividades '17 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
+        <v>Execução do plano de atividades '23 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J62" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K62" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L62" s="0" t="str">
-        <v>11227655</v>
+        <v>11392311</v>
       </c>
       <c r="N62" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O62" s="0" t="str">
-        <v>23/06/2026 01:02:30</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="63" spans="1:15" customFormat="false">
       <c r="A63" s="0" t="str">
-        <v>18 - LIM - TIMS - LIMPEZA DAS SALAS - NORMATEL - ALMOXARIFADO (23/06/2026)</v>
+        <v>24 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 2 (14/07/2026)</v>
       </c>
       <c r="B63" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C63" s="0" t="str">
-        <v>NORMATEL - ALMOXARIFADO</v>
+        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 2</v>
+      </c>
+      <c r="E63" s="0" t="str">
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F63" s="0" t="str">
-        <v>23/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G63" s="0" t="str">
-        <v>23/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H63" s="0" t="str">
-        <v>Execução do plano de atividades '18 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
+        <v>Execução do plano de atividades '24 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J63" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K63" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L63" s="0" t="str">
-        <v>11227656</v>
+        <v>11392312</v>
       </c>
       <c r="N63" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O63" s="0" t="str">
-        <v>23/06/2026 01:02:30</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="64" spans="1:15" customFormat="false">
       <c r="A64" s="0" t="str">
-        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (24/06/2026)</v>
+        <v>25 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 3 (14/07/2026)</v>
       </c>
       <c r="B64" s="0" t="str">
-        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
+        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C64" s="0" t="str">
-        <v>UTGC - GERAL</v>
+        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 3</v>
       </c>
       <c r="E64" s="0" t="str">
-        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
+        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F64" s="0" t="str">
-        <v>24/06/2026 11:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G64" s="0" t="str">
-        <v>24/06/2026 12:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H64" s="0" t="str">
-        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
+        <v>Execução do plano de atividades '25 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J64" s="0" t="str">
-        <v>PROJETO 740 - UTGC</v>
+        <v>PROJETO 739 - UTGSUL</v>
       </c>
       <c r="K64" s="0" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L64" s="0" t="str">
-        <v>11227769</v>
+        <v>11392313</v>
       </c>
       <c r="N64" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O64" s="0" t="str">
-        <v>23/06/2026 01:02:47</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="65" spans="1:15" customFormat="false">
       <c r="A65" s="0" t="str">
-        <v>1 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO MASCULINO - 1 (24/06/2026)</v>
+        <v>26 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 1 (14/07/2026)</v>
       </c>
       <c r="B65" s="0" t="str">
         <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C65" s="0" t="str">
-        <v>K 01 - PORTARIA I - BANHEIRO MASCULINO - 1</v>
+        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 1</v>
       </c>
       <c r="E65" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F65" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G65" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H65" s="0" t="str">
-        <v>Execução do plano de atividades '1 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '26 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J65" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2766,36 +2796,36 @@
         <v>2</v>
       </c>
       <c r="L65" s="0" t="str">
-        <v>11236798</v>
+        <v>11392314</v>
       </c>
       <c r="N65" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O65" s="0" t="str">
-        <v>24/06/2026 01:02:22</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="66" spans="1:15" customFormat="false">
       <c r="A66" s="0" t="str">
-        <v>2 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO FEMININO - 1 (24/06/2026)</v>
+        <v>27 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 2 (14/07/2026)</v>
       </c>
       <c r="B66" s="0" t="str">
         <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C66" s="0" t="str">
-        <v>K 01 - PORTARIA I - BANHEIRO FEMININO - 1</v>
+        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 2</v>
       </c>
       <c r="E66" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F66" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G66" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H66" s="0" t="str">
-        <v>Execução do plano de atividades '2 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '27 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J66" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2804,36 +2834,36 @@
         <v>2</v>
       </c>
       <c r="L66" s="0" t="str">
-        <v>11236799</v>
+        <v>11392315</v>
       </c>
       <c r="N66" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O66" s="0" t="str">
-        <v>24/06/2026 01:02:22</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="67" spans="1:15" customFormat="false">
       <c r="A67" s="0" t="str">
-        <v>3 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO MASCULINO - 2 (24/06/2026)</v>
+        <v>28 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 3 (14/07/2026)</v>
       </c>
       <c r="B67" s="0" t="str">
         <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C67" s="0" t="str">
-        <v>K 01 - PORTARIA I - BANHEIRO MASCULINO - 2</v>
+        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 3</v>
       </c>
       <c r="E67" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F67" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G67" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H67" s="0" t="str">
-        <v>Execução do plano de atividades '3 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '28 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J67" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2842,36 +2872,36 @@
         <v>2</v>
       </c>
       <c r="L67" s="0" t="str">
-        <v>11236800</v>
+        <v>11392316</v>
       </c>
       <c r="N67" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O67" s="0" t="str">
-        <v>24/06/2026 01:02:22</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="68" spans="1:15" customFormat="false">
       <c r="A68" s="0" t="str">
-        <v>4 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 01 - PORTARIA I - BANHEIRO FEMININO - 2 (24/06/2026)</v>
+        <v>29 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 19 - TI / TCOM - BANHEIRO UNISSEX (14/07/2026)</v>
       </c>
       <c r="B68" s="0" t="str">
         <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C68" s="0" t="str">
-        <v>K 01 - PORTARIA I - BANHEIRO FEMININO - 2</v>
+        <v>K 19 - TI / TCOM - BANHEIRO UNISSEX</v>
       </c>
       <c r="E68" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F68" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G68" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H68" s="0" t="str">
-        <v>Execução do plano de atividades '4 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '29 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J68" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2880,36 +2910,36 @@
         <v>2</v>
       </c>
       <c r="L68" s="0" t="str">
-        <v>11236801</v>
+        <v>11392317</v>
       </c>
       <c r="N68" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O68" s="0" t="str">
-        <v>24/06/2026 01:02:22</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="69" spans="1:15" customFormat="false">
       <c r="A69" s="0" t="str">
-        <v>5 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>30 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 31 - PORTARIA II - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B69" s="0" t="str">
         <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C69" s="0" t="str">
-        <v>K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO MASCULINO</v>
+        <v>K 31 - PORTARIA II - BANHEIRO MASCULINO</v>
       </c>
       <c r="E69" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F69" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G69" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H69" s="0" t="str">
-        <v>Execução do plano de atividades '5 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '30 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J69" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2918,36 +2948,36 @@
         <v>2</v>
       </c>
       <c r="L69" s="0" t="str">
-        <v>11236802</v>
+        <v>11392318</v>
       </c>
       <c r="N69" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O69" s="0" t="str">
-        <v>24/06/2026 01:02:22</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="70" spans="1:15" customFormat="false">
       <c r="A70" s="0" t="str">
-        <v>6 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>31 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 31 - PORTARIA II - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B70" s="0" t="str">
         <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C70" s="0" t="str">
-        <v>K 02 - ABRIGO PARA MOTORISTAS - BANHEIRO FEMININO</v>
+        <v>K 31 - PORTARIA II - BANHEIRO FEMININO</v>
       </c>
       <c r="E70" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F70" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G70" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H70" s="0" t="str">
-        <v>Execução do plano de atividades '6 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '31 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J70" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2956,36 +2986,36 @@
         <v>2</v>
       </c>
       <c r="L70" s="0" t="str">
-        <v>11236803</v>
+        <v>11392319</v>
       </c>
       <c r="N70" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O70" s="0" t="str">
-        <v>24/06/2026 01:02:22</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="71" spans="1:15" customFormat="false">
       <c r="A71" s="0" t="str">
-        <v>7 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>1 - LIM - UTGSUL - COPA - K 01 - PORTARIA I - COPA (14/07/2026)</v>
       </c>
       <c r="B71" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C71" s="0" t="str">
-        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO MASCULINO</v>
+        <v>K 01 - PORTARIA I - COPA</v>
       </c>
       <c r="E71" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F71" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G71" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H71" s="0" t="str">
-        <v>Execução do plano de atividades '7 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '1 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J71" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -2994,36 +3024,36 @@
         <v>2</v>
       </c>
       <c r="L71" s="0" t="str">
-        <v>11236804</v>
+        <v>11392320</v>
       </c>
       <c r="N71" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O71" s="0" t="str">
-        <v>24/06/2026 01:02:22</v>
+        <v>14/07/2026 01:02:32</v>
       </c>
     </row>
     <row r="72" spans="1:15" customFormat="false">
       <c r="A72" s="0" t="str">
-        <v>8 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>2 - LIM - UTGSUL - COPA - K 02 - ABRIGO PARA MOTORISTAS - COPA (14/07/2026)</v>
       </c>
       <c r="B72" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C72" s="0" t="str">
-        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - BANHEIRO FEMININO</v>
+        <v>K 02 - ABRIGO PARA MOTORISTAS - COPA</v>
       </c>
       <c r="E72" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F72" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G72" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H72" s="0" t="str">
-        <v>Execução do plano de atividades '8 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '2 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J72" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -3032,36 +3062,36 @@
         <v>2</v>
       </c>
       <c r="L72" s="0" t="str">
-        <v>11236805</v>
+        <v>11392321</v>
       </c>
       <c r="N72" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O72" s="0" t="str">
-        <v>24/06/2026 01:02:22</v>
+        <v>14/07/2026 01:02:33</v>
       </c>
     </row>
     <row r="73" spans="1:15" customFormat="false">
       <c r="A73" s="0" t="str">
-        <v>9 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 04 - VIVÊNCIA - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>3 - LIM - UTGSUL - COPA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - COPA (14/07/2026)</v>
       </c>
       <c r="B73" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C73" s="0" t="str">
-        <v>K 04 - VIVÊNCIA - BANHEIRO MASCULINO</v>
+        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - COPA</v>
       </c>
       <c r="E73" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F73" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G73" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H73" s="0" t="str">
-        <v>Execução do plano de atividades '9 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '3 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J73" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -3070,36 +3100,36 @@
         <v>2</v>
       </c>
       <c r="L73" s="0" t="str">
-        <v>11236806</v>
+        <v>11392322</v>
       </c>
       <c r="N73" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O73" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:33</v>
       </c>
     </row>
     <row r="74" spans="1:15" customFormat="false">
       <c r="A74" s="0" t="str">
-        <v>10 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 04 - VIVÊNCIA - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>4 - LIM - UTGSUL - COPA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - COPA (14/07/2026)</v>
       </c>
       <c r="B74" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C74" s="0" t="str">
-        <v>K 04 - VIVÊNCIA - BANHEIRO FEMININO</v>
+        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - COPA</v>
       </c>
       <c r="E74" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F74" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G74" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H74" s="0" t="str">
-        <v>Execução do plano de atividades '10 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '4 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J74" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -3108,36 +3138,36 @@
         <v>2</v>
       </c>
       <c r="L74" s="0" t="str">
-        <v>11236807</v>
+        <v>11392323</v>
       </c>
       <c r="N74" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O74" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:33</v>
       </c>
     </row>
     <row r="75" spans="1:15" customFormat="false">
       <c r="A75" s="0" t="str">
-        <v>11 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>5 - LIM - UTGSUL - COPA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - COPA (14/07/2026)</v>
       </c>
       <c r="B75" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C75" s="0" t="str">
-        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO MASCULINO</v>
+        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - COPA</v>
       </c>
       <c r="E75" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F75" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G75" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H75" s="0" t="str">
-        <v>Execução do plano de atividades '11 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '5 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J75" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -3146,36 +3176,36 @@
         <v>2</v>
       </c>
       <c r="L75" s="0" t="str">
-        <v>11236808</v>
+        <v>11392324</v>
       </c>
       <c r="N75" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O75" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:33</v>
       </c>
     </row>
     <row r="76" spans="1:15" customFormat="false">
       <c r="A76" s="0" t="str">
-        <v>12 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>6 - LIM - UTGSUL - COPA - K 08 - ALMOXARIFADO - COPA (14/07/2026)</v>
       </c>
       <c r="B76" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C76" s="0" t="str">
-        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - BANHEIRO FEMININO</v>
+        <v>K 08 - ALMOXARIFADO - COPA</v>
       </c>
       <c r="E76" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F76" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G76" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H76" s="0" t="str">
-        <v>Execução do plano de atividades '12 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '6 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J76" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -3184,36 +3214,36 @@
         <v>2</v>
       </c>
       <c r="L76" s="0" t="str">
-        <v>11236809</v>
+        <v>11392325</v>
       </c>
       <c r="N76" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O76" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:33</v>
       </c>
     </row>
     <row r="77" spans="1:15" customFormat="false">
       <c r="A77" s="0" t="str">
-        <v>13 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>7 - LIM - UTGSUL - COPA - K 09 - ALMOXARIFADO - COPA (14/07/2026)</v>
       </c>
       <c r="B77" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C77" s="0" t="str">
-        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO MASCULINO</v>
+        <v>K 09 - ALMOXARIFADO - COPA</v>
       </c>
       <c r="E77" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F77" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G77" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H77" s="0" t="str">
-        <v>Execução do plano de atividades '13 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '7 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J77" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -3222,36 +3252,36 @@
         <v>2</v>
       </c>
       <c r="L77" s="0" t="str">
-        <v>11236810</v>
+        <v>11392326</v>
       </c>
       <c r="N77" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O77" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:33</v>
       </c>
     </row>
     <row r="78" spans="1:15" customFormat="false">
       <c r="A78" s="0" t="str">
-        <v>14 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>8 - LIM - UTGSUL - COPA - K 10 - MANUTENÇÃO - COPA (14/07/2026)</v>
       </c>
       <c r="B78" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C78" s="0" t="str">
-        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - BANHEIRO FEMININO</v>
+        <v>K 10 - MANUTENÇÃO - COPA</v>
       </c>
       <c r="E78" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F78" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G78" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H78" s="0" t="str">
-        <v>Execução do plano de atividades '14 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '8 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J78" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -3260,36 +3290,36 @@
         <v>2</v>
       </c>
       <c r="L78" s="0" t="str">
-        <v>11236811</v>
+        <v>11392327</v>
       </c>
       <c r="N78" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O78" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:33</v>
       </c>
     </row>
     <row r="79" spans="1:15" customFormat="false">
       <c r="A79" s="0" t="str">
-        <v>15 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 08 - ALMOXARIFADO - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>9 - LIM - UTGSUL - COPA - K 11 - LABORATÓRIO - COPA (14/07/2026)</v>
       </c>
       <c r="B79" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - UTGSUL - COPA</v>
       </c>
       <c r="C79" s="0" t="str">
-        <v>K 08 - ALMOXARIFADO - BANHEIRO MASCULINO</v>
+        <v>K 11 - LABORATÓRIO - COPA</v>
       </c>
       <c r="E79" s="0" t="str">
         <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
       </c>
       <c r="F79" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G79" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H79" s="0" t="str">
-        <v>Execução do plano de atividades '15 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '9 - LIM - UTGSUL - COPA'.</v>
       </c>
       <c r="J79" s="0" t="str">
         <v>PROJETO 739 - UTGSUL</v>
@@ -3298,1620 +3328,621 @@
         <v>2</v>
       </c>
       <c r="L79" s="0" t="str">
-        <v>11236812</v>
+        <v>11392328</v>
       </c>
       <c r="N79" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O79" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:33</v>
       </c>
     </row>
     <row r="80" spans="1:15" customFormat="false">
       <c r="A80" s="0" t="str">
-        <v>16 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 08 - ALMOXARIFADO - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (13/08/2026)</v>
       </c>
       <c r="B80" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
       </c>
       <c r="C80" s="0" t="str">
-        <v>K 08 - ALMOXARIFADO - BANHEIRO FEMININO</v>
+        <v>UTGC - GERAL</v>
       </c>
       <c r="E80" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br; heitor.fernandes@normatel.com.br; normatelprojeto740a@gmail.com; normatelprojeto740b@gmail.com; normatelprojetoc@gmail.com</v>
       </c>
       <c r="F80" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>13/08/2026 11:00:00</v>
       </c>
       <c r="G80" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>13/08/2026 12:00:00</v>
       </c>
       <c r="H80" s="0" t="str">
-        <v>Execução do plano de atividades '16 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
       </c>
       <c r="J80" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 740 - UTGC</v>
       </c>
       <c r="K80" s="0" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L80" s="0" t="str">
-        <v>11236813</v>
+        <v>11392452</v>
       </c>
       <c r="N80" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O80" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:54</v>
       </c>
     </row>
     <row r="81" spans="1:15" customFormat="false">
       <c r="A81" s="0" t="str">
-        <v>17 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 09 - ALMOXARIFADO - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>1 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B81" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C81" s="0" t="str">
-        <v>K 09 - ALMOXARIFADO - BANHEIRO MASCULINO</v>
+        <v>GALPÃO BASERV - BANHEIRO MASCULINO</v>
       </c>
       <c r="E81" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>equipelimpezatims@gmail.com; normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F81" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G81" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H81" s="0" t="str">
-        <v>Execução do plano de atividades '17 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '1 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J81" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K81" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L81" s="0" t="str">
-        <v>11236814</v>
+        <v>11392454</v>
       </c>
       <c r="N81" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O81" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="82" spans="1:15" customFormat="false">
       <c r="A82" s="0" t="str">
-        <v>18 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 09 - ALMOXARIFADO - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>2 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B82" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C82" s="0" t="str">
-        <v>K 09 - ALMOXARIFADO - BANHEIRO FEMININO</v>
+        <v>GALPÃO BASERV - BANHEIRO FEMININO</v>
       </c>
       <c r="E82" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>equipelimpezatims@gmail.com; normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F82" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G82" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H82" s="0" t="str">
-        <v>Execução do plano de atividades '18 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '2 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J82" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K82" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L82" s="0" t="str">
-        <v>11236815</v>
+        <v>11392455</v>
       </c>
       <c r="N82" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O82" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="83" spans="1:15" customFormat="false">
       <c r="A83" s="0" t="str">
-        <v>19 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 10 - MANUTENÇÃO - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>3 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO UNISSEX (14/07/2026)</v>
       </c>
       <c r="B83" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C83" s="0" t="str">
-        <v>K 10 - MANUTENÇÃO - BANHEIRO MASCULINO</v>
+        <v>GALPÃO BASERV - BANHEIRO UNISSEX</v>
       </c>
       <c r="E83" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>equipelimpezatims@gmail.com; normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F83" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G83" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H83" s="0" t="str">
-        <v>Execução do plano de atividades '19 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '3 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J83" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K83" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L83" s="0" t="str">
-        <v>11236816</v>
+        <v>11392456</v>
       </c>
       <c r="N83" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O83" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="84" spans="1:15" customFormat="false">
       <c r="A84" s="0" t="str">
-        <v>20 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 10 - MANUTENÇÃO - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>4 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - BRIGADA - CONTÊINER - BANHEIRO UNISSEX (14/07/2026)</v>
       </c>
       <c r="B84" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C84" s="0" t="str">
-        <v>K 10 - MANUTENÇÃO - BANHEIRO FEMININO</v>
+        <v>BRIGADA - CONTÊINER - BANHEIRO UNISSEX</v>
       </c>
       <c r="E84" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>equipelimpezatims@gmail.com; normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F84" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G84" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H84" s="0" t="str">
-        <v>Execução do plano de atividades '20 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '4 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J84" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K84" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L84" s="0" t="str">
-        <v>11236817</v>
+        <v>11392457</v>
       </c>
       <c r="N84" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O84" s="0" t="str">
-        <v>24/06/2026 01:02:23</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="85" spans="1:15" customFormat="false">
       <c r="A85" s="0" t="str">
-        <v>21 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 11 - LABORATÓRIO - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>5 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B85" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C85" s="0" t="str">
-        <v>K 11 - LABORATÓRIO - BANHEIRO MASCULINO</v>
+        <v>IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO MASCULINO</v>
       </c>
       <c r="E85" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>equipelimpezatims@gmail.com; normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F85" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G85" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H85" s="0" t="str">
-        <v>Execução do plano de atividades '21 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '5 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J85" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K85" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L85" s="0" t="str">
-        <v>11236818</v>
+        <v>11392458</v>
       </c>
       <c r="N85" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O85" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="86" spans="1:15" customFormat="false">
       <c r="A86" s="0" t="str">
-        <v>22 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 11 - LABORATÓRIO - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>6 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO FEMININO (14/07/2026)</v>
       </c>
       <c r="B86" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C86" s="0" t="str">
-        <v>K 11 - LABORATÓRIO - BANHEIRO FEMININO</v>
+        <v>IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO FEMININO</v>
       </c>
       <c r="E86" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>equipelimpezatims@gmail.com; normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F86" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G86" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H86" s="0" t="str">
-        <v>Execução do plano de atividades '22 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '6 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J86" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K86" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L86" s="0" t="str">
-        <v>11236819</v>
+        <v>11392459</v>
       </c>
       <c r="N86" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O86" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="87" spans="1:15" customFormat="false">
       <c r="A87" s="0" t="str">
-        <v>23 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 1 (24/06/2026)</v>
+        <v>7 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - GUARITA - BANHEIRO UNISSEX (14/07/2026)</v>
       </c>
       <c r="B87" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C87" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 1</v>
+        <v>IMÓVEL AL 08 - GUARITA - BANHEIRO UNISSEX</v>
       </c>
       <c r="E87" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>equipelimpezatims@gmail.com; normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F87" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G87" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H87" s="0" t="str">
-        <v>Execução do plano de atividades '23 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '7 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J87" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K87" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L87" s="0" t="str">
-        <v>11236820</v>
+        <v>11392460</v>
       </c>
       <c r="N87" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O87" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="88" spans="1:15" customFormat="false">
       <c r="A88" s="0" t="str">
-        <v>24 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 2 (24/06/2026)</v>
+        <v>8 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - VESTIÁRIO - BANHEIRO MASCULINO (14/07/2026)</v>
       </c>
       <c r="B88" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
       </c>
       <c r="C88" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 2</v>
+        <v>VESTIÁRIO - BANHEIRO MASCULINO</v>
       </c>
       <c r="E88" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>equipelimpezatims@gmail.com; normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F88" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G88" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H88" s="0" t="str">
-        <v>Execução do plano de atividades '24 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '8 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
       </c>
       <c r="J88" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K88" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L88" s="0" t="str">
-        <v>11236821</v>
+        <v>11392461</v>
       </c>
       <c r="N88" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O88" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="89" spans="1:15" customFormat="false">
       <c r="A89" s="0" t="str">
-        <v>25 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 3 (24/06/2026)</v>
+        <v>9 - LIM - TIMS - LIMPEZA DO REFEITÓRIO - GALPÃO BASERV - REFEITÓRIO (14/07/2026)</v>
       </c>
       <c r="B89" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - REFEITÓRIO</v>
       </c>
       <c r="C89" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO MASCULINO - 3</v>
+        <v>GALPÃO BASERV - REFEITÓRIO</v>
       </c>
       <c r="E89" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F89" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G89" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H89" s="0" t="str">
-        <v>Execução do plano de atividades '25 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '9 - LIM - TIMS - LIMPEZA DO REFEITÓRIO'.</v>
       </c>
       <c r="J89" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K89" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L89" s="0" t="str">
-        <v>11236822</v>
+        <v>11392462</v>
       </c>
       <c r="N89" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O89" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="90" spans="1:15" customFormat="false">
       <c r="A90" s="0" t="str">
-        <v>26 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 1 (24/06/2026)</v>
+        <v>11 - LIM - TIMS - LIMPEZA DA COPA - GALPÃO BASERV - COPA (14/07/2026)</v>
       </c>
       <c r="B90" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - COPA</v>
       </c>
       <c r="C90" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 1</v>
+        <v>GALPÃO BASERV - COPA</v>
       </c>
       <c r="E90" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F90" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G90" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H90" s="0" t="str">
-        <v>Execução do plano de atividades '26 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '11 - LIM - TIMS - LIMPEZA DA COPA'.</v>
       </c>
       <c r="J90" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K90" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L90" s="0" t="str">
-        <v>11236823</v>
+        <v>11392463</v>
       </c>
       <c r="N90" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O90" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="91" spans="1:15" customFormat="false">
       <c r="A91" s="0" t="str">
-        <v>27 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 2 (24/06/2026)</v>
+        <v>12 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - GUARITA (14/07/2026)</v>
       </c>
       <c r="B91" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
       </c>
       <c r="C91" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 2</v>
+        <v>GALPÃO BASERV - GUARITA</v>
       </c>
       <c r="E91" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F91" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G91" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H91" s="0" t="str">
-        <v>Execução do plano de atividades '27 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '12 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
       </c>
       <c r="J91" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K91" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L91" s="0" t="str">
-        <v>11236824</v>
+        <v>11392464</v>
       </c>
       <c r="N91" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O91" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:55</v>
       </c>
     </row>
     <row r="92" spans="1:15" customFormat="false">
       <c r="A92" s="0" t="str">
-        <v>28 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 14 - ALOJAMENTO - BANHEIRO FEMININO - 3 (24/06/2026)</v>
+        <v>13 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - SALA DE ADMINISTRAÇÃO (14/07/2026)</v>
       </c>
       <c r="B92" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
       </c>
       <c r="C92" s="0" t="str">
-        <v>K 14 - ALOJAMENTO - BANHEIRO FEMININO - 3</v>
+        <v>GALPÃO BASERV - SALA DE ADMINISTRAÇÃO</v>
       </c>
       <c r="E92" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F92" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G92" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H92" s="0" t="str">
-        <v>Execução do plano de atividades '28 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '13 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
       </c>
       <c r="J92" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K92" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L92" s="0" t="str">
-        <v>11236825</v>
+        <v>11392465</v>
       </c>
       <c r="N92" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O92" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:56</v>
       </c>
     </row>
     <row r="93" spans="1:15" customFormat="false">
       <c r="A93" s="0" t="str">
-        <v>29 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 19 - TI / TCOM - BANHEIRO UNISSEX (24/06/2026)</v>
+        <v>14 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - SALA DA BRIGADA (14/07/2026)</v>
       </c>
       <c r="B93" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
       </c>
       <c r="C93" s="0" t="str">
-        <v>K 19 - TI / TCOM - BANHEIRO UNISSEX</v>
+        <v>GALPÃO BASERV - SALA DA BRIGADA</v>
       </c>
       <c r="E93" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F93" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G93" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H93" s="0" t="str">
-        <v>Execução do plano de atividades '29 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '14 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
       </c>
       <c r="J93" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K93" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L93" s="0" t="str">
-        <v>11236826</v>
+        <v>11392466</v>
       </c>
       <c r="N93" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O93" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:56</v>
       </c>
     </row>
     <row r="94" spans="1:15" customFormat="false">
       <c r="A94" s="0" t="str">
-        <v>30 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 31 - PORTARIA II - BANHEIRO MASCULINO (24/06/2026)</v>
+        <v>17 - LIM - TIMS - LIMPEZA DAS SALAS - NORMATEL - SALA DE ADMINISTRAÇÃO (14/07/2026)</v>
       </c>
       <c r="B94" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
       </c>
       <c r="C94" s="0" t="str">
-        <v>K 31 - PORTARIA II - BANHEIRO MASCULINO</v>
+        <v>NORMATEL - SALA DE ADMINISTRAÇÃO</v>
       </c>
       <c r="E94" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F94" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G94" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H94" s="0" t="str">
-        <v>Execução do plano de atividades '30 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '17 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
       </c>
       <c r="J94" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K94" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L94" s="0" t="str">
-        <v>11236827</v>
+        <v>11392467</v>
       </c>
       <c r="N94" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O94" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
+        <v>14/07/2026 01:02:56</v>
       </c>
     </row>
     <row r="95" spans="1:15" customFormat="false">
       <c r="A95" s="0" t="str">
-        <v>31 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA - K 31 - PORTARIA II - BANHEIRO FEMININO (24/06/2026)</v>
+        <v>18 - LIM - TIMS - LIMPEZA DAS SALAS - NORMATEL - ALMOXARIFADO (14/07/2026)</v>
       </c>
       <c r="B95" s="0" t="str">
-        <v>LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA</v>
+        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
       </c>
       <c r="C95" s="0" t="str">
-        <v>K 31 - PORTARIA II - BANHEIRO FEMININO</v>
+        <v>NORMATEL - ALMOXARIFADO</v>
       </c>
       <c r="E95" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
+        <v>normatelmanutencao@gmail.com; normatelprojeto745@gmail.com</v>
       </c>
       <c r="F95" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
+        <v>14/07/2026 01:00:00</v>
       </c>
       <c r="G95" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
+        <v>14/07/2026 21:00:00</v>
       </c>
       <c r="H95" s="0" t="str">
-        <v>Execução do plano de atividades '31 - LIM - UTGSUL - CONSERVAÇÃO E LIMPEZA'.</v>
+        <v>Execução do plano de atividades '18 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
       </c>
       <c r="J95" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
+        <v>PROJETO 745 - TIMS</v>
       </c>
       <c r="K95" s="0" t="str">
         <v>2</v>
       </c>
       <c r="L95" s="0" t="str">
-        <v>11236828</v>
+        <v>11392468</v>
       </c>
       <c r="N95" s="0" t="str">
         <v>A realizar</v>
       </c>
       <c r="O95" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" customFormat="false">
-      <c r="A96" s="0" t="str">
-        <v>1 - LIM - UTGSUL - COPA - K 01 - PORTARIA I - COPA (24/06/2026)</v>
-      </c>
-      <c r="B96" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C96" s="0" t="str">
-        <v>K 01 - PORTARIA I - COPA</v>
-      </c>
-      <c r="E96" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F96" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G96" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H96" s="0" t="str">
-        <v>Execução do plano de atividades '1 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J96" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K96" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L96" s="0" t="str">
-        <v>11236829</v>
-      </c>
-      <c r="N96" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O96" s="0" t="str">
-        <v>24/06/2026 01:02:24</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" customFormat="false">
-      <c r="A97" s="0" t="str">
-        <v>2 - LIM - UTGSUL - COPA - K 02 - ABRIGO PARA MOTORISTAS - COPA (24/06/2026)</v>
-      </c>
-      <c r="B97" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C97" s="0" t="str">
-        <v>K 02 - ABRIGO PARA MOTORISTAS - COPA</v>
-      </c>
-      <c r="E97" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F97" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G97" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H97" s="0" t="str">
-        <v>Execução do plano de atividades '2 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J97" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K97" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L97" s="0" t="str">
-        <v>11236830</v>
-      </c>
-      <c r="N97" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O97" s="0" t="str">
-        <v>24/06/2026 01:02:25</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" customFormat="false">
-      <c r="A98" s="0" t="str">
-        <v>3 - LIM - UTGSUL - COPA - K 03 - CASA DO OPERADOR / CASA DE CONTROLE - COPA (24/06/2026)</v>
-      </c>
-      <c r="B98" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C98" s="0" t="str">
-        <v>K 03 - CASA DO OPERADOR / CASA DE CONTROLE - COPA</v>
-      </c>
-      <c r="E98" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F98" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G98" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H98" s="0" t="str">
-        <v>Execução do plano de atividades '3 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J98" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K98" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L98" s="0" t="str">
-        <v>11236831</v>
-      </c>
-      <c r="N98" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O98" s="0" t="str">
-        <v>24/06/2026 01:02:25</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" customFormat="false">
-      <c r="A99" s="0" t="str">
-        <v>4 - LIM - UTGSUL - COPA - K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - COPA (24/06/2026)</v>
-      </c>
-      <c r="B99" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C99" s="0" t="str">
-        <v>K 05 - ADMINISTRAÇÃO / VESTIÁRIO / REFEITÓRIO - COPA</v>
-      </c>
-      <c r="E99" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F99" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G99" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H99" s="0" t="str">
-        <v>Execução do plano de atividades '4 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J99" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K99" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L99" s="0" t="str">
-        <v>11236832</v>
-      </c>
-      <c r="N99" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O99" s="0" t="str">
-        <v>24/06/2026 01:02:25</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" customFormat="false">
-      <c r="A100" s="0" t="str">
-        <v>5 - LIM - UTGSUL - COPA - K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - COPA (24/06/2026)</v>
-      </c>
-      <c r="B100" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C100" s="0" t="str">
-        <v>K 07 - SEGURANÇA INDUSTRIAL / SETOR MÉDICO - SMS - COPA</v>
-      </c>
-      <c r="E100" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F100" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G100" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H100" s="0" t="str">
-        <v>Execução do plano de atividades '5 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J100" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K100" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L100" s="0" t="str">
-        <v>11236833</v>
-      </c>
-      <c r="N100" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O100" s="0" t="str">
-        <v>24/06/2026 01:02:25</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" customFormat="false">
-      <c r="A101" s="0" t="str">
-        <v>6 - LIM - UTGSUL - COPA - K 08 - ALMOXARIFADO - COPA (24/06/2026)</v>
-      </c>
-      <c r="B101" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C101" s="0" t="str">
-        <v>K 08 - ALMOXARIFADO - COPA</v>
-      </c>
-      <c r="E101" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F101" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G101" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H101" s="0" t="str">
-        <v>Execução do plano de atividades '6 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J101" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K101" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L101" s="0" t="str">
-        <v>11236834</v>
-      </c>
-      <c r="N101" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O101" s="0" t="str">
-        <v>24/06/2026 01:02:25</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" customFormat="false">
-      <c r="A102" s="0" t="str">
-        <v>7 - LIM - UTGSUL - COPA - K 09 - ALMOXARIFADO - COPA (24/06/2026)</v>
-      </c>
-      <c r="B102" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C102" s="0" t="str">
-        <v>K 09 - ALMOXARIFADO - COPA</v>
-      </c>
-      <c r="E102" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F102" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G102" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H102" s="0" t="str">
-        <v>Execução do plano de atividades '7 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J102" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K102" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L102" s="0" t="str">
-        <v>11236835</v>
-      </c>
-      <c r="N102" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O102" s="0" t="str">
-        <v>24/06/2026 01:02:25</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" customFormat="false">
-      <c r="A103" s="0" t="str">
-        <v>8 - LIM - UTGSUL - COPA - K 10 - MANUTENÇÃO - COPA (24/06/2026)</v>
-      </c>
-      <c r="B103" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C103" s="0" t="str">
-        <v>K 10 - MANUTENÇÃO - COPA</v>
-      </c>
-      <c r="E103" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F103" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G103" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H103" s="0" t="str">
-        <v>Execução do plano de atividades '8 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J103" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K103" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L103" s="0" t="str">
-        <v>11236836</v>
-      </c>
-      <c r="N103" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O103" s="0" t="str">
-        <v>24/06/2026 01:02:25</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" customFormat="false">
-      <c r="A104" s="0" t="str">
-        <v>9 - LIM - UTGSUL - COPA - K 11 - LABORATÓRIO - COPA (24/06/2026)</v>
-      </c>
-      <c r="B104" s="0" t="str">
-        <v>LIM - UTGSUL - COPA</v>
-      </c>
-      <c r="C104" s="0" t="str">
-        <v>K 11 - LABORATÓRIO - COPA</v>
-      </c>
-      <c r="E104" s="0" t="str">
-        <v>claudimilsonlimasilva@gmail.com; utgsulnormatel@gmail.com</v>
-      </c>
-      <c r="F104" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G104" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H104" s="0" t="str">
-        <v>Execução do plano de atividades '9 - LIM - UTGSUL - COPA'.</v>
-      </c>
-      <c r="J104" s="0" t="str">
-        <v>PROJETO 739 - UTGSUL</v>
-      </c>
-      <c r="K104" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L104" s="0" t="str">
-        <v>11236837</v>
-      </c>
-      <c r="N104" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O104" s="0" t="str">
-        <v>24/06/2026 01:02:25</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" customFormat="false">
-      <c r="A105" s="0" t="str">
-        <v>19 - LIM - TIMS - LIMPEZA DAS SALAS - IMÓVEL AL 08 - SALA ADMINISTRATIVA (24/06/2026)</v>
-      </c>
-      <c r="B105" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
-      </c>
-      <c r="C105" s="0" t="str">
-        <v>IMÓVEL AL 08 - SALA ADMINISTRATIVA</v>
-      </c>
-      <c r="F105" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G105" s="0" t="str">
-        <v>25/06/2026 00:20:00</v>
-      </c>
-      <c r="H105" s="0" t="str">
-        <v>Execução do plano de atividades '19 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
-      </c>
-      <c r="J105" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K105" s="0" t="str">
-        <v>1</v>
-      </c>
-      <c r="L105" s="0" t="str">
-        <v>11236860</v>
-      </c>
-      <c r="N105" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O105" s="0" t="str">
-        <v>24/06/2026 01:02:27</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" customFormat="false">
-      <c r="A106" s="0" t="str">
-        <v>1 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO MASCULINO (24/06/2026)</v>
-      </c>
-      <c r="B106" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C106" s="0" t="str">
-        <v>GALPÃO BASERV - BANHEIRO MASCULINO</v>
-      </c>
-      <c r="E106" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
-      </c>
-      <c r="F106" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G106" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H106" s="0" t="str">
-        <v>Execução do plano de atividades '1 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
-      </c>
-      <c r="J106" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K106" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L106" s="0" t="str">
-        <v>11236861</v>
-      </c>
-      <c r="N106" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O106" s="0" t="str">
-        <v>24/06/2026 01:02:27</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" customFormat="false">
-      <c r="A107" s="0" t="str">
-        <v>2 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO FEMININO (24/06/2026)</v>
-      </c>
-      <c r="B107" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C107" s="0" t="str">
-        <v>GALPÃO BASERV - BANHEIRO FEMININO</v>
-      </c>
-      <c r="E107" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
-      </c>
-      <c r="F107" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G107" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H107" s="0" t="str">
-        <v>Execução do plano de atividades '2 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
-      </c>
-      <c r="J107" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K107" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L107" s="0" t="str">
-        <v>11236862</v>
-      </c>
-      <c r="N107" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O107" s="0" t="str">
-        <v>24/06/2026 01:02:27</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" customFormat="false">
-      <c r="A108" s="0" t="str">
-        <v>3 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - GALPÃO BASERV - BANHEIRO UNISSEX (24/06/2026)</v>
-      </c>
-      <c r="B108" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C108" s="0" t="str">
-        <v>GALPÃO BASERV - BANHEIRO UNISSEX</v>
-      </c>
-      <c r="E108" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
-      </c>
-      <c r="F108" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G108" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H108" s="0" t="str">
-        <v>Execução do plano de atividades '3 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
-      </c>
-      <c r="J108" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K108" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L108" s="0" t="str">
-        <v>11236863</v>
-      </c>
-      <c r="N108" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O108" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" customFormat="false">
-      <c r="A109" s="0" t="str">
-        <v>4 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - BRIGADA - CONTÊINER - BANHEIRO UNISSEX (24/06/2026)</v>
-      </c>
-      <c r="B109" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C109" s="0" t="str">
-        <v>BRIGADA - CONTÊINER - BANHEIRO UNISSEX</v>
-      </c>
-      <c r="E109" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
-      </c>
-      <c r="F109" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G109" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H109" s="0" t="str">
-        <v>Execução do plano de atividades '4 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
-      </c>
-      <c r="J109" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K109" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L109" s="0" t="str">
-        <v>11236864</v>
-      </c>
-      <c r="N109" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O109" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" customFormat="false">
-      <c r="A110" s="0" t="str">
-        <v>5 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO MASCULINO (24/06/2026)</v>
-      </c>
-      <c r="B110" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C110" s="0" t="str">
-        <v>IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO MASCULINO</v>
-      </c>
-      <c r="E110" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
-      </c>
-      <c r="F110" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G110" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H110" s="0" t="str">
-        <v>Execução do plano de atividades '5 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
-      </c>
-      <c r="J110" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K110" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L110" s="0" t="str">
-        <v>11236865</v>
-      </c>
-      <c r="N110" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O110" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" customFormat="false">
-      <c r="A111" s="0" t="str">
-        <v>6 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO FEMININO (24/06/2026)</v>
-      </c>
-      <c r="B111" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C111" s="0" t="str">
-        <v>IMÓVEL AL 08 - SALA ADMINISTRATIVA - BANHEIRO FEMININO</v>
-      </c>
-      <c r="E111" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
-      </c>
-      <c r="F111" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G111" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H111" s="0" t="str">
-        <v>Execução do plano de atividades '6 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
-      </c>
-      <c r="J111" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K111" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L111" s="0" t="str">
-        <v>11236866</v>
-      </c>
-      <c r="N111" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O111" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" customFormat="false">
-      <c r="A112" s="0" t="str">
-        <v>7 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - IMÓVEL AL 08 - GUARITA - BANHEIRO UNISSEX (24/06/2026)</v>
-      </c>
-      <c r="B112" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C112" s="0" t="str">
-        <v>IMÓVEL AL 08 - GUARITA - BANHEIRO UNISSEX</v>
-      </c>
-      <c r="E112" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
-      </c>
-      <c r="F112" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G112" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H112" s="0" t="str">
-        <v>Execução do plano de atividades '7 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
-      </c>
-      <c r="J112" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K112" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L112" s="0" t="str">
-        <v>11236867</v>
-      </c>
-      <c r="N112" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O112" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" customFormat="false">
-      <c r="A113" s="0" t="str">
-        <v>8 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA - VESTIÁRIO - BANHEIRO MASCULINO (24/06/2026)</v>
-      </c>
-      <c r="B113" s="0" t="str">
-        <v>LIM - TIMS - CONSERVAÇÃO E LIMPEZA</v>
-      </c>
-      <c r="C113" s="0" t="str">
-        <v>VESTIÁRIO - BANHEIRO MASCULINO</v>
-      </c>
-      <c r="E113" s="0" t="str">
-        <v>equipelimpezatims@gmail.com</v>
-      </c>
-      <c r="F113" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G113" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H113" s="0" t="str">
-        <v>Execução do plano de atividades '8 - LIM - TIMS - CONSERVAÇÃO E LIMPEZA'.</v>
-      </c>
-      <c r="J113" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K113" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L113" s="0" t="str">
-        <v>11236868</v>
-      </c>
-      <c r="N113" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O113" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" customFormat="false">
-      <c r="A114" s="0" t="str">
-        <v>9 - LIM - TIMS - LIMPEZA DO REFEITÓRIO - GALPÃO BASERV - REFEITÓRIO (24/06/2026)</v>
-      </c>
-      <c r="B114" s="0" t="str">
-        <v>LIM - TIMS - REFEITÓRIO</v>
-      </c>
-      <c r="C114" s="0" t="str">
-        <v>GALPÃO BASERV - REFEITÓRIO</v>
-      </c>
-      <c r="F114" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G114" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H114" s="0" t="str">
-        <v>Execução do plano de atividades '9 - LIM - TIMS - LIMPEZA DO REFEITÓRIO'.</v>
-      </c>
-      <c r="J114" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K114" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L114" s="0" t="str">
-        <v>11236869</v>
-      </c>
-      <c r="N114" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O114" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" customFormat="false">
-      <c r="A115" s="0" t="str">
-        <v>10 - LIM - TIMS - LIMPEZA DO REFEITÓRIO - IMÓVEL AL 08 - REFEITÓRIO (24/06/2026)</v>
-      </c>
-      <c r="B115" s="0" t="str">
-        <v>LIM - TIMS - REFEITÓRIO</v>
-      </c>
-      <c r="C115" s="0" t="str">
-        <v>IMÓVEL AL 08 - REFEITÓRIO</v>
-      </c>
-      <c r="F115" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G115" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H115" s="0" t="str">
-        <v>Execução do plano de atividades '10 - LIM - TIMS - LIMPEZA DO REFEITÓRIO'.</v>
-      </c>
-      <c r="J115" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K115" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L115" s="0" t="str">
-        <v>11236870</v>
-      </c>
-      <c r="N115" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O115" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" customFormat="false">
-      <c r="A116" s="0" t="str">
-        <v>11 - LIM - TIMS - LIMPEZA DA COPA - GALPÃO BASERV - COPA (24/06/2026)</v>
-      </c>
-      <c r="B116" s="0" t="str">
-        <v>LIM - TIMS - COPA</v>
-      </c>
-      <c r="C116" s="0" t="str">
-        <v>GALPÃO BASERV - COPA</v>
-      </c>
-      <c r="F116" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G116" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H116" s="0" t="str">
-        <v>Execução do plano de atividades '11 - LIM - TIMS - LIMPEZA DA COPA'.</v>
-      </c>
-      <c r="J116" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K116" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L116" s="0" t="str">
-        <v>11236871</v>
-      </c>
-      <c r="N116" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O116" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" customFormat="false">
-      <c r="A117" s="0" t="str">
-        <v>12 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - GUARITA (24/06/2026)</v>
-      </c>
-      <c r="B117" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
-      </c>
-      <c r="C117" s="0" t="str">
-        <v>GALPÃO BASERV - GUARITA</v>
-      </c>
-      <c r="F117" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G117" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H117" s="0" t="str">
-        <v>Execução do plano de atividades '12 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
-      </c>
-      <c r="J117" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K117" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L117" s="0" t="str">
-        <v>11236872</v>
-      </c>
-      <c r="N117" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O117" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" customFormat="false">
-      <c r="A118" s="0" t="str">
-        <v>13 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - SALA DE ADMINISTRAÇÃO (24/06/2026)</v>
-      </c>
-      <c r="B118" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
-      </c>
-      <c r="C118" s="0" t="str">
-        <v>GALPÃO BASERV - SALA DE ADMINISTRAÇÃO</v>
-      </c>
-      <c r="F118" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G118" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H118" s="0" t="str">
-        <v>Execução do plano de atividades '13 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
-      </c>
-      <c r="J118" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K118" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L118" s="0" t="str">
-        <v>11236873</v>
-      </c>
-      <c r="N118" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O118" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" customFormat="false">
-      <c r="A119" s="0" t="str">
-        <v>14 - LIM - TIMS - LIMPEZA DAS SALAS - GALPÃO BASERV - SALA DA BRIGADA (24/06/2026)</v>
-      </c>
-      <c r="B119" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
-      </c>
-      <c r="C119" s="0" t="str">
-        <v>GALPÃO BASERV - SALA DA BRIGADA</v>
-      </c>
-      <c r="F119" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G119" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H119" s="0" t="str">
-        <v>Execução do plano de atividades '14 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
-      </c>
-      <c r="J119" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K119" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L119" s="0" t="str">
-        <v>11236874</v>
-      </c>
-      <c r="N119" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O119" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" customFormat="false">
-      <c r="A120" s="0" t="str">
-        <v>17 - LIM - TIMS - LIMPEZA DAS SALAS - NORMATEL - SALA DE ADMINISTRAÇÃO (24/06/2026)</v>
-      </c>
-      <c r="B120" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
-      </c>
-      <c r="C120" s="0" t="str">
-        <v>NORMATEL - SALA DE ADMINISTRAÇÃO</v>
-      </c>
-      <c r="F120" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G120" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H120" s="0" t="str">
-        <v>Execução do plano de atividades '17 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
-      </c>
-      <c r="J120" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K120" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L120" s="0" t="str">
-        <v>11236875</v>
-      </c>
-      <c r="N120" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O120" s="0" t="str">
-        <v>24/06/2026 01:02:28</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" customFormat="false">
-      <c r="A121" s="0" t="str">
-        <v>18 - LIM - TIMS - LIMPEZA DAS SALAS - NORMATEL - ALMOXARIFADO (24/06/2026)</v>
-      </c>
-      <c r="B121" s="0" t="str">
-        <v>LIM - TIMS - LIMPEZA DAS SALAS</v>
-      </c>
-      <c r="C121" s="0" t="str">
-        <v>NORMATEL - ALMOXARIFADO</v>
-      </c>
-      <c r="F121" s="0" t="str">
-        <v>24/06/2026 01:00:00</v>
-      </c>
-      <c r="G121" s="0" t="str">
-        <v>24/06/2026 21:00:00</v>
-      </c>
-      <c r="H121" s="0" t="str">
-        <v>Execução do plano de atividades '18 - LIM - TIMS - LIMPEZA DAS SALAS'.</v>
-      </c>
-      <c r="J121" s="0" t="str">
-        <v>PROJETO 745 - TIMS</v>
-      </c>
-      <c r="K121" s="0" t="str">
-        <v>2</v>
-      </c>
-      <c r="L121" s="0" t="str">
-        <v>11236876</v>
-      </c>
-      <c r="N121" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O121" s="0" t="str">
-        <v>24/06/2026 01:02:29</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" customFormat="false">
-      <c r="A122" s="0" t="str">
-        <v>Inspeção diária de Qualidade - Período da Manha - UTGC - GERAL (25/06/2026)</v>
-      </c>
-      <c r="B122" s="0" t="str">
-        <v>QLD - UTGC - RELATÓRIO DE INSPEÇÃO</v>
-      </c>
-      <c r="C122" s="0" t="str">
-        <v>UTGC - GERAL</v>
-      </c>
-      <c r="E122" s="0" t="str">
-        <v>gabriel.almeida@normatel.com.br; glaudstone.silva@normatel.com.br</v>
-      </c>
-      <c r="F122" s="0" t="str">
-        <v>25/06/2026 11:00:00</v>
-      </c>
-      <c r="G122" s="0" t="str">
-        <v>25/06/2026 12:00:00</v>
-      </c>
-      <c r="H122" s="0" t="str">
-        <v>Execução do plano de atividades 'Inspeção diária de Qualidade - Período da Manha'.</v>
-      </c>
-      <c r="J122" s="0" t="str">
-        <v>PROJETO 740 - UTGC</v>
-      </c>
-      <c r="K122" s="0" t="str">
-        <v>3</v>
-      </c>
-      <c r="L122" s="0" t="str">
-        <v>11236989</v>
-      </c>
-      <c r="N122" s="0" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O122" s="0" t="str">
-        <v>24/06/2026 01:02:46</v>
+        <v>14/07/2026 01:02:56</v>
       </c>
     </row>
   </sheetData>
